--- a/templates/[대한지리학회]기초번호판설치점검_주간보고_템플릿.xlsx
+++ b/templates/[대한지리학회]기초번호판설치점검_주간보고_템플릿.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\JavaScript DEV\public-보고서\서버에 업로드_20260819_현재\addr.chk.2026-main\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{930ACD41-9D9F-4A24-904B-D50CB45C24F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9B1D8B2-42CE-4656-B147-2C8DB07B139D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="주간보고내용" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -112,126 +112,7 @@
     <t>기준일자</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>입력</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">] </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>예</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>: 2026-07-10 (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>매주 목요일</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
     <t>보고기간</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>입력</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">] </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>예</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>: 2026-07-04 ~ 2026-07-10</t>
-    </r>
   </si>
   <si>
     <t>사업기간</t>
@@ -431,6 +312,14 @@
       </rPr>
       <t>특이사항 등</t>
     </r>
+  </si>
+  <si>
+    <t>[입력] 예: 2026-08-20 (매주 목요일 기준으로 날짜 작성)</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>[입력] 예: 2026-08-14 ~ 2026-08-20</t>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -609,15 +498,6 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -628,6 +508,15 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -902,219 +791,224 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="27.75" customHeight="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
     </row>
     <row r="4" spans="1:6" ht="15" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
+      <c r="B4" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
     </row>
     <row r="5" spans="1:6" ht="15" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
+        <v>6</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1">
       <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:6" ht="18" customHeight="1">
+      <c r="A7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+    </row>
+    <row r="8" spans="1:6" ht="18" customHeight="1">
+      <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-    </row>
-    <row r="7" spans="1:6" ht="18" customHeight="1">
-      <c r="A7" s="8" t="s">
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+    </row>
+    <row r="9" spans="1:6" ht="79.5" customHeight="1">
+      <c r="A9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-    </row>
-    <row r="8" spans="1:6" ht="18" customHeight="1">
-      <c r="A8" s="6" t="s">
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+    </row>
+    <row r="14" spans="1:6" ht="18" customHeight="1">
+      <c r="A14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-    </row>
-    <row r="9" spans="1:6" ht="79.5" customHeight="1">
-      <c r="A9" s="5" t="s">
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+    </row>
+    <row r="15" spans="1:6" ht="79.5" customHeight="1">
+      <c r="A15" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-    </row>
-    <row r="14" spans="1:6" ht="18" customHeight="1">
-      <c r="A14" s="6" t="s">
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+    </row>
+    <row r="20" spans="1:6" ht="18" customHeight="1">
+      <c r="A20" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-    </row>
-    <row r="15" spans="1:6" ht="79.5" customHeight="1">
-      <c r="A15" s="5" t="s">
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+    </row>
+    <row r="21" spans="1:6" ht="79.5" customHeight="1">
+      <c r="A21" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="5"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-    </row>
-    <row r="20" spans="1:6" ht="18" customHeight="1">
-      <c r="A20" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-    </row>
-    <row r="21" spans="1:6" ht="79.5" customHeight="1">
-      <c r="A21" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
     </row>
     <row r="22" spans="1:6">
-      <c r="A22" s="5"/>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
     </row>
     <row r="23" spans="1:6">
-      <c r="A23" s="5"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="5"/>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B5:F5"/>
     <mergeCell ref="A15:F18"/>
     <mergeCell ref="A20:F20"/>
     <mergeCell ref="A21:F24"/>
@@ -1123,11 +1017,6 @@
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="A9:F12"/>
     <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="B5:F5"/>
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
